--- a/ImportUserTestFile.xlsx
+++ b/ImportUserTestFile.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SWP391_SSMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>Parent Email</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>Female</t>
-  </si>
-  <si>
-    <t>12A2</t>
   </si>
   <si>
     <t>nguyenhangnhathuy1@gmail.com</t>
@@ -452,7 +449,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1">
         <v>1782223123</v>
@@ -470,7 +467,7 @@
         <v>37889</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -498,7 +495,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1">
         <v>1782223123</v>
@@ -507,7 +504,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>14</v>
@@ -516,7 +513,7 @@
         <v>37889</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
